--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>320459</v>
+        <v>4172247</v>
       </c>
       <c r="B2" t="n">
-        <v>89608</v>
+        <v>95511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1101</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Toftmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572326.9251568295</v>
+        <v>572226.8525733686</v>
       </c>
       <c r="R2" t="n">
-        <v>6619875.140378467</v>
+        <v>6619873.707280044</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +754,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-11-05</t>
+          <t>2011-05-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-11-05</t>
+          <t>2011-05-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -774,12 +783,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Ungskog på torvbrytningsområde</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Torvmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79558050</v>
+        <v>320459</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
+        <v>89608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,28 +822,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Toftmossen, Vstm</t>
@@ -871,7 +876,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
+          <t>2011-11-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -881,7 +886,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
+          <t>2011-11-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -895,18 +900,17 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av björk</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Tall, murken låga</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100195745</v>
+        <v>79558050</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
+        <v>94121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,42 +940,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -980,13 +972,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572281.7324929546</v>
+        <v>572326.9251568295</v>
       </c>
       <c r="R4" t="n">
-        <v>6619885.368150346</v>
+        <v>6619875.140378467</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,7 +1002,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1020,7 +1012,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1040,12 +1032,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog, inslag av björk</t>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>I mosstäcke</t>
+          <t>Tall, murken låga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100195762</v>
+        <v>100195745</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
+        <v>96334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,30 +1067,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1168,6 +1172,11 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Gammal barrblandskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>I mosstäcke</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1185,64 +1194,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104436824</v>
+        <v>100195762</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
+        <v>95519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Toftmossen (knärot), Vstm</t>
+          <t>Toftmossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572277.6895627538</v>
+        <v>572281.7324929546</v>
       </c>
       <c r="R6" t="n">
-        <v>6619885.289860292</v>
+        <v>6619885.368150346</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,11 +1266,6 @@
           <t>Sura</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>U-Sur-0476</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>2022-04-23</t>
@@ -1298,26 +1292,163 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>mosstäcke, gammal barrblandskog, inslag av björk</t>
+          <t>Gammal barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104436824</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Toftmossen (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572277.6895627538</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619885.289860292</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>U-Sur-0476</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>mosstäcke, gammal barrblandskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Bo Eriksson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4172247</v>
+        <v>79558050</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Toftmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572226.8525733686</v>
+        <v>572327</v>
       </c>
       <c r="R2" t="n">
-        <v>6619873.707280044</v>
+        <v>6619875</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-05-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,17 +758,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Ungskog på torvbrytningsområde</t>
+          <t>Barrblandskog, inslag av björk</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Torvmark</t>
+          <t>Tall, murken låga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,12 +790,7 @@
         <v>320459</v>
       </c>
       <c r="B3" t="n">
-        <v>89608</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572326.9251568295</v>
+        <v>572327</v>
       </c>
       <c r="R3" t="n">
-        <v>6619875.140378467</v>
+        <v>6619875</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -879,19 +855,9 @@
           <t>2011-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-11-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79558050</v>
+        <v>133648602</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,41 +905,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>102987</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Toftmossen, Vstm</t>
+          <t>Toftmossen, Toftmossen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572326.9251568295</v>
+        <v>572282</v>
       </c>
       <c r="R4" t="n">
-        <v>6619875.140378467</v>
+        <v>6619828</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +971,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,84 +995,64 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog, inslag av björk</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Tall, murken låga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100195745</v>
+        <v>134320430</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103019</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1111,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572281.7324929546</v>
+        <v>572289</v>
       </c>
       <c r="R5" t="n">
-        <v>6619885.368150346</v>
+        <v>6619829</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,22 +1090,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,71 +1114,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog, inslag av björk</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>I mosstäcke</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100195762</v>
+        <v>100195745</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1238,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572281.7324929546</v>
+        <v>572282</v>
       </c>
       <c r="R6" t="n">
-        <v>6619885.368150346</v>
+        <v>6619885</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,19 +1216,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,6 +1234,11 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>Gammal barrblandskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>I mosstäcke</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,12 +1259,7 @@
         <v>104436824</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572277.6895627538</v>
+        <v>572278</v>
       </c>
       <c r="R7" t="n">
-        <v>6619885.289860292</v>
+        <v>6619885</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,19 +1343,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,6 +1378,225 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4172247</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Toftmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572227</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6619874</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2011-05-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2011-05-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Ungskog på torvbrytningsområde</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Torvmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100195762</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Toftmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572282</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619885</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38172-2024 artfynd.xlsx
+++ b/artfynd/A 38172-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79558050</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/320459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133648602</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134320430</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100195745</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104436824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4172247</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1597,8 +1637,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100195762</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>